--- a/data/trans_camb/P13_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P13_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 2,12</t>
+          <t>-3,25; 2,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 2,16</t>
+          <t>-3,31; 2,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 2,64</t>
+          <t>-2,41; 2,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 1,85</t>
+          <t>-4,77; 2,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 2,34</t>
+          <t>-4,4; 2,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,26</t>
+          <t>-4,5; 1,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,16</t>
+          <t>-3,16; 1,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,43</t>
+          <t>-3,01; 1,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,39</t>
+          <t>-2,34; 1,46</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,4; 72,03</t>
+          <t>-59,0; 73,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-58,75; 78,03</t>
+          <t>-61,44; 80,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,78; 90,97</t>
+          <t>-42,83; 109,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-64,74; 62,43</t>
+          <t>-67,67; 77,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,29; 79,75</t>
+          <t>-63,7; 60,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,55; 36,53</t>
+          <t>-59,32; 44,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,1; 36,13</t>
+          <t>-52,66; 30,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,35; 38,32</t>
+          <t>-52,44; 34,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-40,99; 38,04</t>
+          <t>-41,84; 40,85</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 5,37</t>
+          <t>0,52; 5,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,66</t>
+          <t>-0,59; 3,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 4,0</t>
+          <t>-0,04; 4,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 7,26</t>
+          <t>0,45; 7,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,78</t>
+          <t>-2,74; 1,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 4,2</t>
+          <t>-0,26; 4,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,05</t>
+          <t>1,11; 5,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,27</t>
+          <t>-0,99; 2,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 3,51</t>
+          <t>0,47; 3,58</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 1017,38</t>
+          <t>-2,36; 1502,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-40,61; 793,8</t>
+          <t>-50,33; 898,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 791,21</t>
+          <t>-19,31; 1086,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 500,87</t>
+          <t>0,17; 519,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,22; 148,79</t>
+          <t>-76,84; 149,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,0; 319,16</t>
+          <t>-18,3; 318,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,95; 412,52</t>
+          <t>32,82; 404,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,76; 191,8</t>
+          <t>-43,15; 174,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 292,73</t>
+          <t>11,79; 315,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,22</t>
+          <t>1,47; 5,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,77</t>
+          <t>-0,13; 4,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 4,12</t>
+          <t>-1,68; 4,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 7,22</t>
+          <t>-3,75; 7,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 8,07</t>
+          <t>-4,69; 8,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 8,57</t>
+          <t>-2,19; 9,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,59</t>
+          <t>1,06; 5,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,48</t>
+          <t>-0,15; 4,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 4,65</t>
+          <t>-2,07; 4,54</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,0; 488,16</t>
+          <t>43,82; 551,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,15; 425,29</t>
+          <t>-10,84; 403,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,01; 302,89</t>
+          <t>-53,1; 364,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 163,15</t>
+          <t>-36,75; 193,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,3; 188,02</t>
+          <t>-46,53; 204,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 187,29</t>
+          <t>-23,24; 218,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,13; 241,57</t>
+          <t>20,49; 242,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 191,42</t>
+          <t>-8,64; 182,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-43,56; 181,09</t>
+          <t>-43,13; 169,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,47</t>
+          <t>-0,19; 3,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,39</t>
+          <t>-1,81; 1,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,53</t>
+          <t>1,01; 4,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 5,34</t>
+          <t>0,15; 5,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,71</t>
+          <t>-0,9; 3,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 2,35</t>
+          <t>-3,16; 2,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,64</t>
+          <t>0,59; 3,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,75</t>
+          <t>-0,85; 1,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 3,15</t>
+          <t>-0,27; 3,09</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 122,02</t>
+          <t>-5,7; 116,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-42,33; 51,33</t>
+          <t>-42,68; 48,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,29; 153,17</t>
+          <t>22,44; 155,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 138,99</t>
+          <t>0,38; 151,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,84; 94,65</t>
+          <t>-15,89; 109,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,56; 57,02</t>
+          <t>-47,59; 71,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,54; 105,61</t>
+          <t>12,22; 104,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 47,52</t>
+          <t>-18,33; 54,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 89,75</t>
+          <t>-4,45; 84,5</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 1,49</t>
+          <t>-4,16; 2,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 2,78</t>
+          <t>-3,23; 2,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 5,89</t>
+          <t>-1,27; 5,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,32; 11,54</t>
+          <t>5,59; 11,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 4,71</t>
+          <t>0,11; 4,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 7,24</t>
+          <t>1,73; 7,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,79</t>
+          <t>2,44; 6,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,32</t>
+          <t>-0,5; 3,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,21</t>
+          <t>1,85; 5,94</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-57,48; 52,08</t>
+          <t>-59,8; 72,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-44,92; 97,72</t>
+          <t>-46,7; 90,37</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 186,3</t>
+          <t>-20,72; 186,63</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>90,0; 406,72</t>
+          <t>100,53; 381,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 164,39</t>
+          <t>2,22; 175,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,85; 245,2</t>
+          <t>33,44; 272,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,35; 203,52</t>
+          <t>44,12; 204,39</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 100,95</t>
+          <t>-9,36; 104,83</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>32,76; 184,66</t>
+          <t>35,41; 185,87</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 5,36</t>
+          <t>-0,96; 5,59</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,31; -0,2</t>
+          <t>-4,21; -0,03</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 1,32</t>
+          <t>-3,56; 1,55</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,25</t>
+          <t>3,17; 7,96</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,93</t>
+          <t>-1,83; 2,03</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,52</t>
+          <t>1,49; 5,7</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,85; 6,97</t>
+          <t>2,89; 6,69</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,19</t>
+          <t>-1,94; 1,23</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,96</t>
+          <t>0,63; 3,95</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-37,5; 418,99</t>
+          <t>-34,37; 489,3</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 47,0</t>
+          <t>-100,0; 68,96</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-83,53; 119,15</t>
+          <t>-84,84; 147,08</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>48,38; 174,21</t>
+          <t>49,35; 179,65</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 42,68</t>
+          <t>-28,45; 43,61</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>25,5; 119,23</t>
+          <t>23,88; 132,41</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>48,81; 167,7</t>
+          <t>50,08; 157,86</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-37,16; 31,27</t>
+          <t>-34,58; 29,41</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7,71; 96,27</t>
+          <t>10,2; 95,77</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,53</t>
+          <t>0,34; 2,39</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,14</t>
+          <t>-0,59; 1,27</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,78</t>
+          <t>0,49; 2,79</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,75</t>
+          <t>3,25; 5,63</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,92</t>
+          <t>-0,38; 1,82</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,07</t>
+          <t>0,49; 3,02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,77</t>
+          <t>2,18; 3,75</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,22</t>
+          <t>-0,19; 1,21</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,7</t>
+          <t>0,95; 2,69</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>13,48; 90,38</t>
+          <t>9,37; 85,21</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 40,49</t>
+          <t>-16,14; 47,45</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13,7; 101,22</t>
+          <t>13,94; 95,87</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>59,54; 131,98</t>
+          <t>60,12; 129,93</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 44,01</t>
+          <t>-7,89; 40,69</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,11; 71,33</t>
+          <t>9,45; 68,08</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>48,86; 101,53</t>
+          <t>50,83; 102,6</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 33,49</t>
+          <t>-4,43; 31,64</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>20,17; 73,05</t>
+          <t>22,11; 72,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P13_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P13_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-1,13</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-0,41</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 2,2</t>
+          <t>-3,3; 2,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 2,06</t>
+          <t>-3,55; 1,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 2,97</t>
+          <t>-2,63; 2,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 2,01</t>
+          <t>-4,83; 1,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 2,11</t>
+          <t>-4,55; 2,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 1,28</t>
+          <t>-4,19; 1,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,02</t>
+          <t>-3,24; 0,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,24</t>
+          <t>-2,91; 1,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,46</t>
+          <t>-2,51; 1,35</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-26,75%</t>
+          <t>-21,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-9,84%</t>
+          <t>-8,81%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,0; 73,85</t>
+          <t>-58,87; 73,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-61,44; 80,21</t>
+          <t>-60,91; 66,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,83; 109,91</t>
+          <t>-44,82; 83,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-67,67; 77,0</t>
+          <t>-67,64; 64,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,7; 60,71</t>
+          <t>-63,35; 74,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,32; 44,21</t>
+          <t>-56,08; 60,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,66; 30,17</t>
+          <t>-55,5; 25,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,44; 34,58</t>
+          <t>-51,58; 41,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-41,84; 40,85</t>
+          <t>-43,09; 37,65</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,08</t>
+          <t>1,96</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>1,97</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>1,92</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,55</t>
+          <t>0,51; 5,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,83</t>
+          <t>-0,49; 3,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 4,2</t>
+          <t>-0,18; 3,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 7,09</t>
+          <t>0,44; 6,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 1,83</t>
+          <t>-2,63; 1,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,27</t>
+          <t>-0,95; 4,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,06</t>
+          <t>1,0; 5,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,13</t>
+          <t>-0,86; 2,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,58</t>
+          <t>0,32; 3,49</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152,11%</t>
+          <t>143,09%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>103,48%</t>
+          <t>100,46%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1502,89</t>
+          <t>-2,44; 1090,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,33; 898,55</t>
+          <t>-32,78; 795,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,31; 1086,85</t>
+          <t>-29,28; 722,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 519,96</t>
+          <t>-1,58; 502,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,84; 149,21</t>
+          <t>-75,87; 162,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,3; 318,86</t>
+          <t>-26,71; 314,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,82; 404,56</t>
+          <t>31,43; 422,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,15; 174,1</t>
+          <t>-32,48; 210,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,79; 315,54</t>
+          <t>6,83; 341,22</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,55</t>
+          <t>3,17</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>3,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,72</t>
+          <t>1,45; 5,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 4,41</t>
+          <t>-0,01; 4,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 4,47</t>
+          <t>1,47; 6,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 7,65</t>
+          <t>-4,1; 7,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 8,46</t>
+          <t>-5,16; 8,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 9,23</t>
+          <t>-2,42; 8,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,48</t>
+          <t>1,06; 5,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 4,21</t>
+          <t>-0,17; 4,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 4,54</t>
+          <t>1,55; 6,13</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>190,86%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>117,1%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43,82; 551,4</t>
+          <t>46,82; 574,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 403,16</t>
+          <t>-9,0; 416,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-53,1; 364,56</t>
+          <t>41,71; 656,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-36,75; 193,53</t>
+          <t>-40,62; 167,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,53; 204,41</t>
+          <t>-51,69; 174,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 218,11</t>
+          <t>-27,62; 206,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,49; 242,26</t>
+          <t>23,74; 261,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 182,45</t>
+          <t>-4,2; 193,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-43,13; 169,12</t>
+          <t>36,59; 266,68</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>3,02</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>2,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 3,34</t>
+          <t>-0,15; 3,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,35</t>
+          <t>-1,84; 1,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,6</t>
+          <t>1,16; 4,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 5,56</t>
+          <t>0,24; 5,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,93</t>
+          <t>-1,09; 3,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 2,79</t>
+          <t>-0,64; 3,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,58</t>
+          <t>0,58; 3,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,83</t>
+          <t>-0,92; 1,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,09</t>
+          <t>1,02; 3,82</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>58,71%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 116,06</t>
+          <t>-6,23; 113,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-42,68; 48,53</t>
+          <t>-43,8; 44,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,44; 155,28</t>
+          <t>23,55; 162,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 151,29</t>
+          <t>3,46; 145,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,89; 109,45</t>
+          <t>-17,8; 98,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-47,59; 71,18</t>
+          <t>-12,47; 91,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,22; 104,32</t>
+          <t>11,52; 100,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 54,82</t>
+          <t>-19,3; 50,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 84,5</t>
+          <t>20,91; 112,58</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>1,72</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>6,04</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,02</t>
+          <t>4,3</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 2,15</t>
+          <t>-4,07; 1,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 2,78</t>
+          <t>-3,24; 2,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 5,81</t>
+          <t>-1,83; 4,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,59; 11,46</t>
+          <t>5,36; 11,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,95</t>
+          <t>0,07; 5,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,73; 7,22</t>
+          <t>3,52; 8,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,44; 6,71</t>
+          <t>2,34; 6,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,24</t>
+          <t>-0,48; 3,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,94</t>
+          <t>2,46; 6,1</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>120,32%</t>
+          <t>149,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-59,8; 72,68</t>
+          <t>-59,99; 61,29</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,7; 90,37</t>
+          <t>-48,02; 86,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 186,63</t>
+          <t>-26,64; 152,44</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>100,53; 381,54</t>
+          <t>100,95; 401,97</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,22; 175,99</t>
+          <t>-2,64; 171,12</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,44; 272,73</t>
+          <t>55,2; 289,42</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,12; 204,39</t>
+          <t>42,36; 198,88</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 104,83</t>
+          <t>-10,43; 91,65</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>35,41; 185,87</t>
+          <t>44,08; 178,66</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,82</t>
+          <t>-0,73</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,48</t>
+          <t>3,34</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>2,36</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 5,59</t>
+          <t>-1,27; 5,7</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,21; -0,03</t>
+          <t>-4,56; -0,08</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 1,55</t>
+          <t>-3,4; 1,67</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,96</t>
+          <t>3,13; 7,8</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,03</t>
+          <t>-1,97; 1,88</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,7</t>
+          <t>1,38; 5,39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,69</t>
+          <t>2,9; 7,09</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,23</t>
+          <t>-2,15; 1,17</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,95</t>
+          <t>0,59; 4,02</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-32,09%</t>
+          <t>-28,39%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>48,09%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-34,37; 489,3</t>
+          <t>-37,59; 429,42</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 68,96</t>
+          <t>-100,0; 75,3</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-84,84; 147,08</t>
+          <t>-81,95; 164,82</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>49,35; 179,65</t>
+          <t>44,78; 161,1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 43,61</t>
+          <t>-31,03; 39,92</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,88; 132,41</t>
+          <t>19,18; 117,93</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>50,08; 157,86</t>
+          <t>49,4; 173,55</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-34,58; 29,41</t>
+          <t>-37,81; 29,09</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>10,2; 95,77</t>
+          <t>10,14; 97,79</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>2,09</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,96</t>
+          <t>2,58</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>2,35</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,39</t>
+          <t>0,47; 2,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,27</t>
+          <t>-0,67; 1,22</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,79</t>
+          <t>1,18; 3,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,25; 5,63</t>
+          <t>3,25; 5,83</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,82</t>
+          <t>-0,38; 1,77</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,02</t>
+          <t>1,59; 3,58</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,75</t>
+          <t>2,16; 3,69</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,21</t>
+          <t>-0,17; 1,24</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,69</t>
+          <t>1,64; 3,07</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>58,32%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>9,37; 85,21</t>
+          <t>12,46; 96,34</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 47,45</t>
+          <t>-17,69; 46,66</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13,94; 95,87</t>
+          <t>32,78; 118,52</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>60,12; 129,93</t>
+          <t>58,97; 133,07</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 40,69</t>
+          <t>-7,02; 40,44</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,45; 68,08</t>
+          <t>29,03; 85,54</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>50,83; 102,6</t>
+          <t>48,01; 99,06</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 31,64</t>
+          <t>-4,05; 33,96</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>22,11; 72,9</t>
+          <t>37,98; 84,24</t>
         </is>
       </c>
     </row>
